--- a/public/config/client/ItemConfig.xlsx
+++ b/public/config/client/ItemConfig.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,10 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,7 +499,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_path</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>description</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
@@ -533,6 +551,21 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>resource_ref</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>resource_ref</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -570,7 +603,22 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>CS</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -607,7 +655,22 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>图标资源</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>模型资源</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>描述</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>策划备注(不导出)</t>
         </is>
       </c>
     </row>
@@ -634,7 +697,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>ui/icon_coin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>游戏通用货币</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>基础货币</t>
         </is>
       </c>
     </row>
@@ -661,9 +735,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>ui/icon_diamond</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>稀有货币</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -688,9 +769,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>ui/icon_potion_red</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>恢复50点生命值</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -715,9 +803,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>ui/icon_potion_blue</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>恢复30点魔法值</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -742,7 +837,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>ui/icon_sword_001</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>wp/sword_001</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>一把普通的铁剑</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>新手装备</t>
         </is>
       </c>
     </row>
